--- a/Reports/Invoice_Report.xlsx
+++ b/Reports/Invoice_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/37edf83e19019baf/Documents/UiPath/InvoiceAutomation/Reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{9BD67052-66F8-41B5-AA41-367FBD117C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{716C6399-9C26-40BD-8E07-F385EA217AA9}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{9BD67052-66F8-41B5-AA41-367FBD117C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C15AE7C4-4967-431C-8EAC-1EB132ADE4FA}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="2328" windowWidth="17280" windowHeight="8880" xr2:uid="{2FED9B06-6B8C-4BBC-9B4B-16162135B321}"/>
   </bookViews>
